--- a/data/processed/Panel_RRUI_NDVI_MaySep_Climate_AprOct_Livestock.xlsx
+++ b/data/processed/Panel_RRUI_NDVI_MaySep_Climate_AprOct_Livestock.xlsx
@@ -452,7 +452,7 @@
         <v>20.7513829440447</v>
       </c>
       <c r="I2" t="n">
-        <v>100.9918</v>
+        <v>85.3283</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>20.9043752716146</v>
       </c>
       <c r="I3" t="n">
-        <v>75.4766</v>
+        <v>66.0095</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         <v>20.1580283361941</v>
       </c>
       <c r="I4" t="n">
-        <v>86.0594</v>
+        <v>72.2526</v>
       </c>
     </row>
     <row r="5">
@@ -539,7 +539,7 @@
         <v>21.1778556470097</v>
       </c>
       <c r="I5" t="n">
-        <v>73.5816</v>
+        <v>60.0768</v>
       </c>
     </row>
     <row r="6">
@@ -568,7 +568,7 @@
         <v>20.0947690726851</v>
       </c>
       <c r="I6" t="n">
-        <v>37.144</v>
+        <v>32.5535</v>
       </c>
     </row>
     <row r="7">
@@ -597,7 +597,7 @@
         <v>18.6979795930057</v>
       </c>
       <c r="I7" t="n">
-        <v>111.776</v>
+        <v>94.1192</v>
       </c>
     </row>
     <row r="8">
@@ -626,7 +626,7 @@
         <v>18.9225764820862</v>
       </c>
       <c r="I8" t="n">
-        <v>78.6576</v>
+        <v>69.1286</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +655,7 @@
         <v>18.3064596458788</v>
       </c>
       <c r="I9" t="n">
-        <v>97.2316</v>
+        <v>80.7886</v>
       </c>
     </row>
     <row r="10">
@@ -684,7 +684,7 @@
         <v>19.1412312310766</v>
       </c>
       <c r="I10" t="n">
-        <v>82.2452</v>
+        <v>67.3432</v>
       </c>
     </row>
     <row r="11">
@@ -713,7 +713,7 @@
         <v>18.0639828587373</v>
       </c>
       <c r="I11" t="n">
-        <v>40.6638</v>
+        <v>35.6961</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         <v>18.350067508252</v>
       </c>
       <c r="I12" t="n">
-        <v>122.3442</v>
+        <v>102.5991</v>
       </c>
     </row>
     <row r="13">
@@ -771,7 +771,7 @@
         <v>19.0746887936444</v>
       </c>
       <c r="I13" t="n">
-        <v>91.7318</v>
+        <v>81.3153</v>
       </c>
     </row>
     <row r="14">
@@ -800,7 +800,7 @@
         <v>18.0249025422624</v>
       </c>
       <c r="I14" t="n">
-        <v>109.094</v>
+        <v>89.6015</v>
       </c>
     </row>
     <row r="15">
@@ -829,7 +829,7 @@
         <v>18.960836182355</v>
       </c>
       <c r="I15" t="n">
-        <v>90.795</v>
+        <v>73.9275</v>
       </c>
     </row>
     <row r="16">
@@ -858,7 +858,7 @@
         <v>18.0759024702697</v>
       </c>
       <c r="I16" t="n">
-        <v>44.9312</v>
+        <v>39.601</v>
       </c>
     </row>
     <row r="17">
@@ -887,7 +887,7 @@
         <v>18.5457175577073</v>
       </c>
       <c r="I17" t="n">
-        <v>129.5594</v>
+        <v>108.7421</v>
       </c>
     </row>
     <row r="18">
@@ -916,7 +916,7 @@
         <v>19.2658271271021</v>
       </c>
       <c r="I18" t="n">
-        <v>93.0064</v>
+        <v>82.2632</v>
       </c>
     </row>
     <row r="19">
@@ -945,7 +945,7 @@
         <v>18.4867031427612</v>
       </c>
       <c r="I19" t="n">
-        <v>118.5368</v>
+        <v>97.4458</v>
       </c>
     </row>
     <row r="20">
@@ -974,7 +974,7 @@
         <v>19.222202592629</v>
       </c>
       <c r="I20" t="n">
-        <v>93.3528</v>
+        <v>76.4482</v>
       </c>
     </row>
     <row r="21">
@@ -1003,7 +1003,7 @@
         <v>18.4567335132223</v>
       </c>
       <c r="I21" t="n">
-        <v>49.992</v>
+        <v>43.8126</v>
       </c>
     </row>
     <row r="22">
@@ -1032,7 +1032,7 @@
         <v>18.324490657481</v>
       </c>
       <c r="I22" t="n">
-        <v>135.3466</v>
+        <v>114.2014</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1061,7 @@
         <v>19.2916342386433</v>
       </c>
       <c r="I23" t="n">
-        <v>95.3546</v>
+        <v>84.8409</v>
       </c>
     </row>
     <row r="24">
@@ -1090,7 +1090,7 @@
         <v>18.4055910221763</v>
       </c>
       <c r="I24" t="n">
-        <v>129.1348</v>
+        <v>107.1935</v>
       </c>
     </row>
     <row r="25">
@@ -1119,7 +1119,7 @@
         <v>19.0820688178797</v>
       </c>
       <c r="I25" t="n">
-        <v>96.9774</v>
+        <v>80.3299</v>
       </c>
     </row>
     <row r="26">
@@ -1148,7 +1148,7 @@
         <v>18.358057522709</v>
       </c>
       <c r="I26" t="n">
-        <v>54.4718</v>
+        <v>48.2643</v>
       </c>
     </row>
     <row r="27">
@@ -1177,7 +1177,7 @@
         <v>18.2736147483267</v>
       </c>
       <c r="I27" t="n">
-        <v>148.36</v>
+        <v>126.48</v>
       </c>
     </row>
     <row r="28">
@@ -1206,7 +1206,7 @@
         <v>18.9799293924718</v>
       </c>
       <c r="I28" t="n">
-        <v>100.64</v>
+        <v>91.41</v>
       </c>
     </row>
     <row r="29">
@@ -1235,7 +1235,7 @@
         <v>18.0045784135731</v>
       </c>
       <c r="I29" t="n">
-        <v>139.3</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="30">
@@ -1264,7 +1264,7 @@
         <v>18.9674856320297</v>
       </c>
       <c r="I30" t="n">
-        <v>104</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="31">
@@ -1293,7 +1293,7 @@
         <v>17.9012756020899</v>
       </c>
       <c r="I31" t="n">
-        <v>61.38</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="32">
@@ -1322,7 +1322,7 @@
         <v>18.9253212589935</v>
       </c>
       <c r="I32" t="n">
-        <v>156.72</v>
+        <v>134.41</v>
       </c>
     </row>
     <row r="33">
@@ -1351,7 +1351,7 @@
         <v>19.6043533501991</v>
       </c>
       <c r="I33" t="n">
-        <v>101.74</v>
+        <v>92.48</v>
       </c>
     </row>
     <row r="34">
@@ -1380,7 +1380,7 @@
         <v>18.8305807301537</v>
       </c>
       <c r="I34" t="n">
-        <v>144.76</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="35">
@@ -1409,7 +1409,7 @@
         <v>19.654482128607</v>
       </c>
       <c r="I35" t="n">
-        <v>108.78</v>
+        <v>92.73</v>
       </c>
     </row>
     <row r="36">
@@ -1438,7 +1438,7 @@
         <v>19.0166789251411</v>
       </c>
       <c r="I36" t="n">
-        <v>67</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="37">
@@ -1467,7 +1467,7 @@
         <v>18.5589450509354</v>
       </c>
       <c r="I37" t="n">
-        <v>160.84</v>
+        <v>138.62</v>
       </c>
     </row>
     <row r="38">
@@ -1496,7 +1496,7 @@
         <v>19.0832435331514</v>
       </c>
       <c r="I38" t="n">
-        <v>105.56</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="39">
@@ -1525,7 +1525,7 @@
         <v>18.2777759048909</v>
       </c>
       <c r="I39" t="n">
-        <v>151.52</v>
+        <v>128.42</v>
       </c>
     </row>
     <row r="40">
@@ -1554,7 +1554,7 @@
         <v>19.2224795291083</v>
       </c>
       <c r="I40" t="n">
-        <v>111.58</v>
+        <v>96.27</v>
       </c>
     </row>
     <row r="41">
@@ -1583,7 +1583,7 @@
         <v>18.2455224866702</v>
       </c>
       <c r="I41" t="n">
-        <v>68.76</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="42">
@@ -1612,7 +1612,7 @@
         <v>18.6751738257821</v>
       </c>
       <c r="I42" t="n">
-        <v>170.58</v>
+        <v>148.99</v>
       </c>
     </row>
     <row r="43">
@@ -1641,7 +1641,7 @@
         <v>19.3836594041495</v>
       </c>
       <c r="I43" t="n">
-        <v>115.6</v>
+        <v>106.62</v>
       </c>
     </row>
     <row r="44">
@@ -1670,7 +1670,7 @@
         <v>18.5085238146211</v>
       </c>
       <c r="I44" t="n">
-        <v>172.48</v>
+        <v>147.46</v>
       </c>
     </row>
     <row r="45">
@@ -1699,7 +1699,7 @@
         <v>19.399090497606</v>
       </c>
       <c r="I45" t="n">
-        <v>126.24</v>
+        <v>110.22</v>
       </c>
     </row>
     <row r="46">
@@ -1728,7 +1728,7 @@
         <v>18.46108444999</v>
       </c>
       <c r="I46" t="n">
-        <v>71.92</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="47">
@@ -1757,7 +1757,7 @@
         <v>20.0869286820129</v>
       </c>
       <c r="I47" t="n">
-        <v>180.96</v>
+        <v>159.18</v>
       </c>
     </row>
     <row r="48">
@@ -1786,7 +1786,7 @@
         <v>19.7041151313351</v>
       </c>
       <c r="I48" t="n">
-        <v>122.14</v>
+        <v>113.33</v>
       </c>
     </row>
     <row r="49">
@@ -1815,7 +1815,7 @@
         <v>19.133872998858</v>
       </c>
       <c r="I49" t="n">
-        <v>177.76</v>
+        <v>151.72</v>
       </c>
     </row>
     <row r="50">
@@ -1844,7 +1844,7 @@
         <v>19.9914971579171</v>
       </c>
       <c r="I50" t="n">
-        <v>131.72</v>
+        <v>116.24</v>
       </c>
     </row>
     <row r="51">
@@ -1873,7 +1873,7 @@
         <v>18.9586042212377</v>
       </c>
       <c r="I51" t="n">
-        <v>79.38</v>
+        <v>73.54</v>
       </c>
     </row>
     <row r="52">
@@ -1902,7 +1902,7 @@
         <v>18.6320797224067</v>
       </c>
       <c r="I52" t="n">
-        <v>201.58</v>
+        <v>179.48</v>
       </c>
     </row>
     <row r="53">
@@ -1931,7 +1931,7 @@
         <v>19.2908049878579</v>
       </c>
       <c r="I53" t="n">
-        <v>143.24</v>
+        <v>133.34</v>
       </c>
     </row>
     <row r="54">
@@ -1960,7 +1960,7 @@
         <v>18.3170925044744</v>
       </c>
       <c r="I54" t="n">
-        <v>196.26</v>
+        <v>168.51</v>
       </c>
     </row>
     <row r="55">
@@ -1989,7 +1989,7 @@
         <v>19.3275524505507</v>
       </c>
       <c r="I55" t="n">
-        <v>145.24</v>
+        <v>128.89</v>
       </c>
     </row>
     <row r="56">
@@ -2018,7 +2018,7 @@
         <v>18.180748134678</v>
       </c>
       <c r="I56" t="n">
-        <v>98.02</v>
+        <v>90.74</v>
       </c>
     </row>
     <row r="57">
@@ -2047,7 +2047,7 @@
         <v>19.0159901718085</v>
       </c>
       <c r="I57" t="n">
-        <v>193.16</v>
+        <v>173.76</v>
       </c>
     </row>
     <row r="58">
@@ -2076,7 +2076,7 @@
         <v>19.507576693574</v>
       </c>
       <c r="I58" t="n">
-        <v>130.04</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="59">
@@ -2105,7 +2105,7 @@
         <v>18.444971138669</v>
       </c>
       <c r="I59" t="n">
-        <v>192.62</v>
+        <v>167.79</v>
       </c>
     </row>
     <row r="60">
@@ -2134,7 +2134,7 @@
         <v>19.5562335260466</v>
       </c>
       <c r="I60" t="n">
-        <v>136.78</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="61">
@@ -2163,7 +2163,7 @@
         <v>18.3974001234628</v>
       </c>
       <c r="I61" t="n">
-        <v>88.28</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="62">
@@ -2192,7 +2192,7 @@
         <v>19.0718734755048</v>
       </c>
       <c r="I62" t="n">
-        <v>236.22</v>
+        <v>214.38</v>
       </c>
     </row>
     <row r="63">
@@ -2221,7 +2221,7 @@
         <v>20.0082773807869</v>
       </c>
       <c r="I63" t="n">
-        <v>158.32</v>
+        <v>148.28</v>
       </c>
     </row>
     <row r="64">
@@ -2250,7 +2250,7 @@
         <v>19.1335766535827</v>
       </c>
       <c r="I64" t="n">
-        <v>236.3</v>
+        <v>206.36</v>
       </c>
     </row>
     <row r="65">
@@ -2279,7 +2279,7 @@
         <v>19.772910584884</v>
       </c>
       <c r="I65" t="n">
-        <v>156.2842</v>
+        <v>142.0521</v>
       </c>
     </row>
     <row r="66">
@@ -2308,7 +2308,7 @@
         <v>19.2944298999446</v>
       </c>
       <c r="I66" t="n">
-        <v>109.2</v>
+        <v>101.18</v>
       </c>
     </row>
   </sheetData>
